--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.7568905131894</v>
+        <v>2.235494708393277</v>
       </c>
       <c r="D2" t="n">
-        <v>10.54751155486449</v>
+        <v>1.71397062766548</v>
       </c>
       <c r="E2" t="n">
-        <v>11.05773477651762</v>
+        <v>1.796881901184114</v>
       </c>
       <c r="F2" t="n">
-        <v>12.66856646077434</v>
+        <v>2.058642049875831</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.96956548219227</v>
+        <v>3.895054390856243</v>
       </c>
       <c r="D3" t="n">
-        <v>23.52619198622945</v>
+        <v>3.823006197762285</v>
       </c>
       <c r="E3" t="n">
-        <v>11.05773477651762</v>
+        <v>1.796881901184114</v>
       </c>
       <c r="F3" t="n">
-        <v>12.66856646077434</v>
+        <v>2.058642049875831</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.58894306597476</v>
+        <v>6.595703248220898</v>
       </c>
       <c r="D4" t="n">
-        <v>41.44754580953596</v>
+        <v>6.735226194049594</v>
       </c>
       <c r="E4" t="n">
-        <v>11.05773477651762</v>
+        <v>1.796881901184114</v>
       </c>
       <c r="F4" t="n">
-        <v>12.66856646077434</v>
+        <v>2.058642049875831</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
